--- a/DataTables/DetailText/剧情/004老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004老师来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A5BDE9-5EBE-4C2A-9A60-B21074B0CF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B3AE60-8D8F-49E1-945C-2B9D0192E9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2753" yWindow="2813" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -536,7 +525,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -550,7 +539,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -571,7 +560,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -669,7 +658,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -950,15 +939,15 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="83.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="83.73046875" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/004老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004老师来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B3AE60-8D8F-49E1-945C-2B9D0192E9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D54177-873F-4081-842C-3A8AC68BC235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2753" yWindow="2813" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
   <si>
     <t>StoryID</t>
   </si>
@@ -514,6 +525,14 @@
   </si>
   <si>
     <t>老师来访</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>人生在世不止考取科举一条路，你能找到一条适合自己的路，为师很欣慰。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>承蒙老师教诲，学生愿精进医术一生治病救人。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -525,7 +544,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -539,7 +558,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -560,7 +579,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -621,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -656,9 +675,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -939,15 +961,15 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="83.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="83.75" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1203,18 +1225,34 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="I10" s="12" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="2"/>
+      <c r="A11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="I11" s="12" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6"/>

--- a/DataTables/DetailText/剧情/004老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004老师来访.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D54177-873F-4081-842C-3A8AC68BC235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2F7826-BE53-4F8D-827F-CECBD3374141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,10 +292,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>李东壁</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>left</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -533,6 +529,10 @@
   </si>
   <si>
     <t>承蒙老师教诲，学生愿精进医术一生治病救人。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>李东璧</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -640,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -677,6 +677,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1004,10 +1007,10 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -1031,10 +1034,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -1056,10 +1059,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -1081,10 +1084,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -1106,10 +1109,10 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="C6" s="1">
         <v>5</v>
@@ -1117,24 +1120,24 @@
       <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="C7" s="3">
         <v>6</v>
@@ -1151,15 +1154,15 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
@@ -1167,24 +1170,24 @@
       <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="C9" s="1">
         <v>8</v>
@@ -1201,15 +1204,15 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
@@ -1226,15 +1229,15 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="C11" s="3">
         <v>10</v>
@@ -1242,16 +1245,16 @@
       <c r="D11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:9">

--- a/DataTables/DetailText/剧情/004老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004老师来访.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2F7826-BE53-4F8D-827F-CECBD3374141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86739207-B0BB-4B1F-9C23-5AB1A1B3D9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="30">
   <si>
     <t>StoryID</t>
   </si>
@@ -533,6 +533,10 @@
   </si>
   <si>
     <t>李东璧</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Hide</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -961,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
@@ -971,12 +975,13 @@
     <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="83.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="4"/>
+    <col min="8" max="8" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -998,14 +1003,17 @@
       <c r="G1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
@@ -1025,14 +1033,15 @@
         <v>9</v>
       </c>
       <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="5" t="s">
         <v>24</v>
       </c>
@@ -1053,11 +1062,12 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2"/>
+      <c r="J3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
@@ -1078,11 +1088,12 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="2"/>
+      <c r="J4" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="5" t="s">
         <v>24</v>
       </c>
@@ -1103,11 +1114,12 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="2"/>
+      <c r="J5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="5" t="s">
         <v>24</v>
       </c>
@@ -1128,11 +1140,12 @@
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="2"/>
+      <c r="J6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" s="5" t="s">
         <v>24</v>
       </c>
@@ -1153,11 +1166,12 @@
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" s="5" t="s">
         <v>24</v>
       </c>
@@ -1178,11 +1192,12 @@
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="3"/>
+      <c r="J8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9" s="5" t="s">
         <v>24</v>
       </c>
@@ -1203,11 +1218,12 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="3"/>
+      <c r="J9" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10" s="5" t="s">
         <v>24</v>
       </c>
@@ -1228,11 +1244,12 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="3"/>
+      <c r="J10" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10">
       <c r="A11" s="5" t="s">
         <v>24</v>
       </c>
@@ -1253,11 +1270,12 @@
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="3"/>
+      <c r="J11" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="3"/>
@@ -1267,8 +1285,9 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:10">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="3"/>
@@ -1278,6 +1297,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/004老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004老师来访.xlsx
@@ -1,42 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86739207-B0BB-4B1F-9C23-5AB1A1B3D9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A2DF3A-CBC3-4B8C-A8AF-BD02A9C7D806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Story" sheetId="3" r:id="rId1"/>
+    <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="42">
   <si>
     <t>StoryID</t>
   </si>
@@ -59,11 +49,11 @@
     <t>dialogue</t>
   </si>
   <si>
-    <t>StoryName</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>PortraitSide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>left</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -79,6 +69,56 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>Hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>StoryName</t>
+  </si>
+  <si>
+    <t>TriggerType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerScene</t>
+  </si>
+  <si>
+    <t>TriggerDay</t>
+  </si>
+  <si>
+    <t>Reputation</t>
+  </si>
+  <si>
+    <t>EntryId</t>
+  </si>
+  <si>
+    <t>NpcID</t>
+  </si>
+  <si>
+    <t>TriggerNpcID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayOnce</t>
+  </si>
+  <si>
+    <t>ReturnScene</t>
+  </si>
+  <si>
+    <t>SortIndex</t>
+  </si>
+  <si>
+    <t>scene_enter</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>night</t>
+  </si>
+  <si>
+    <t>顾问</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
       <t>res://Assets/Background/clinic</t>
     </r>
@@ -115,7 +155,29 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>顾问</t>
+    <r>
+      <t>言</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>闻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>兄别来无恙啊。</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -128,32 +190,6 @@
   </si>
   <si>
     <r>
-      <t>言</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>闻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>兄别来无恙啊。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -292,7 +328,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>left</t>
+    <t>李东璧</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -516,28 +552,18 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>人生在世不止考取科举一条路，你能找到一条适合自己的路，为师很欣慰。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>承蒙老师教诲，学生愿精进医术一生治病救人。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>004</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>老师来访</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>人生在世不止考取科举一条路，你能找到一条适合自己的路，为师很欣慰。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>承蒙老师教诲，学生愿精进医术一生治病救人。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>李东璧</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Hide</t>
-    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -548,7 +574,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -562,7 +588,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -583,10 +609,17 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -595,15 +628,8 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -613,6 +639,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,7 +682,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -661,12 +699,6 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -676,18 +708,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -964,340 +1007,353 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
+  <cols>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.06640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.59765625" customWidth="1"/>
+    <col min="11" max="11" width="13.53125" customWidth="1"/>
+    <col min="12" max="12" width="10.73046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="18">
+      <c r="A2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18">
+      <c r="C3" s="12"/>
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" spans="1:12" ht="18">
+      <c r="C4" s="12"/>
+    </row>
+    <row r="5" spans="1:12" ht="18">
+      <c r="C5" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.9296875" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="1">
-        <v>4</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="1">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="3">
-        <v>6</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="1">
-        <v>7</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="C11" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1">
-        <v>9</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="3">
-        <v>10</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="H11" s="16" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/004老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004老师来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A2DF3A-CBC3-4B8C-A8AF-BD02A9C7D806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC95D36-F96C-4496-93F5-6C8C4C5F84D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
   <si>
     <t>StoryID</t>
   </si>
@@ -564,6 +575,10 @@
   </si>
   <si>
     <t>老师来访</t>
+  </si>
+  <si>
+    <t>dim</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -574,7 +589,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -588,7 +603,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -609,7 +624,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -730,7 +745,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1009,23 +1024,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.06640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.59765625" customWidth="1"/>
-    <col min="11" max="11" width="13.53125" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18">
+    <row r="1" spans="1:12">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1063,7 +1078,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18">
+    <row r="2" spans="1:12">
       <c r="A2" s="5" t="s">
         <v>40</v>
       </c>
@@ -1095,14 +1110,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18">
+    <row r="3" spans="1:12">
       <c r="C3" s="12"/>
       <c r="J3" s="13"/>
     </row>
-    <row r="4" spans="1:12" ht="18">
+    <row r="4" spans="1:12">
       <c r="C4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="18">
+    <row r="5" spans="1:12">
       <c r="C5" s="12"/>
     </row>
   </sheetData>
@@ -1116,14 +1131,14 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.9296875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1167,7 +1182,9 @@
         <v>9</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="F2" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="G2" s="2" t="s">
         <v>27</v>
       </c>
@@ -1189,7 +1206,9 @@
         <v>11</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="F3" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
         <v>30</v>
@@ -1209,7 +1228,9 @@
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="F4" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="14" t="s">
         <v>31</v>
@@ -1229,7 +1250,9 @@
         <v>11</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="F5" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
         <v>32</v>
@@ -1249,7 +1272,9 @@
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
         <v>34</v>
@@ -1269,7 +1294,9 @@
         <v>9</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="F7" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
         <v>35</v>
@@ -1289,7 +1316,9 @@
         <v>8</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="F8" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
         <v>36</v>
@@ -1309,7 +1338,9 @@
         <v>9</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
         <v>37</v>
@@ -1329,7 +1360,9 @@
         <v>9</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="F10" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="G10" s="3"/>
       <c r="H10" s="16" t="s">
         <v>38</v>
@@ -1349,7 +1382,9 @@
         <v>8</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="F11" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="G11" s="3"/>
       <c r="H11" s="16" t="s">
         <v>39</v>

--- a/DataTables/DetailText/剧情/004老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004老师来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC95D36-F96C-4496-93F5-6C8C4C5F84D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35442741-635E-4ACD-B831-143F99748563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="44">
   <si>
     <t>StoryID</t>
   </si>
@@ -579,17 +568,20 @@
   <si>
     <t>dim</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ClinicNpcPortraitPath</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -603,7 +595,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -624,7 +616,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -640,6 +632,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -726,8 +726,6 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -743,9 +741,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1023,24 +1023,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" customWidth="1"/>
+    <col min="12" max="12" width="13.46484375" customWidth="1"/>
+    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13" ht="18">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1053,32 +1054,35 @@
       <c r="D1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="16" t="s">
         <v>20</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13" ht="18">
       <c r="A2" s="5" t="s">
         <v>40</v>
       </c>
@@ -1100,25 +1104,26 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1" t="b">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="C3" s="12"/>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="C4" s="12"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="C5" s="12"/>
+    <row r="3" spans="1:13" ht="18">
+      <c r="C3" s="10"/>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="1:13" ht="18">
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:13" ht="18">
+      <c r="C5" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -1131,14 +1136,14 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1232,7 +1237,7 @@
         <v>42</v>
       </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="12" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1265,7 +1270,7 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="13" t="s">
         <v>33</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -1309,7 +1314,7 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="13" t="s">
         <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -1364,7 +1369,7 @@
         <v>42</v>
       </c>
       <c r="G10" s="3"/>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="14" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1375,7 +1380,7 @@
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="13" t="s">
         <v>33</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -1386,7 +1391,7 @@
         <v>42</v>
       </c>
       <c r="G11" s="3"/>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="14" t="s">
         <v>39</v>
       </c>
     </row>

--- a/DataTables/DetailText/剧情/004老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004老师来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35442741-635E-4ACD-B831-143F99748563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8EC963-B2C4-4332-A3EB-866AD2695F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -120,42 +131,6 @@
   </si>
   <si>
     <r>
-      <t>res://Assets/Background/clinic</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>spring</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.png</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
       <t>言</t>
     </r>
     <r>
@@ -571,6 +546,22 @@
   </si>
   <si>
     <t>ClinicNpcPortraitPath</t>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>004/004.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -581,7 +572,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -595,7 +586,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -616,7 +607,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -745,7 +736,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1024,24 +1015,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.59765625" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" customWidth="1"/>
-    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18">
+    <row r="1" spans="1:13">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1070,7 +1061,7 @@
         <v>20</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>21</v>
@@ -1082,12 +1073,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18">
+    <row r="2" spans="1:13">
       <c r="A2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
@@ -1115,14 +1106,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18">
+    <row r="3" spans="1:13">
       <c r="C3" s="10"/>
       <c r="K3" s="11"/>
     </row>
-    <row r="4" spans="1:13" ht="18">
+    <row r="4" spans="1:13">
       <c r="C4" s="10"/>
     </row>
-    <row r="5" spans="1:13" ht="18">
+    <row r="5" spans="1:13">
       <c r="C5" s="10"/>
     </row>
   </sheetData>
@@ -1136,14 +1127,14 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1188,13 +1179,13 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1205,18 +1196,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1234,11 +1225,11 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1249,18 +1240,18 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1271,18 +1262,18 @@
         <v>6</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1300,11 +1291,11 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1315,18 +1306,18 @@
         <v>6</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1344,11 +1335,11 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1366,11 +1357,11 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1381,18 +1372,18 @@
         <v>6</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/004老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004老师来访.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8EC963-B2C4-4332-A3EB-866AD2695F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C77DF17-B8A8-45E8-8129-A770C3D66C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="45">
   <si>
     <t>StoryID</t>
   </si>
@@ -562,13 +562,17 @@
       <t>004/004.png</t>
     </r>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -688,7 +692,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -734,6 +738,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1014,8 +1021,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
@@ -1023,16 +1030,17 @@
     <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1052,28 +1060,31 @@
         <v>17</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>39</v>
       </c>
@@ -1092,29 +1103,78 @@
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="5"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="b">
+      <c r="K2" s="1"/>
+      <c r="L2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="C3" s="10"/>
-      <c r="K3" s="11"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="G3" s="17"/>
+      <c r="L3" s="11"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="C4" s="10"/>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="C5" s="10"/>
+      <c r="G5" s="17"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G6" s="17"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G7" s="17"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G8" s="17"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G9" s="17"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G10" s="17"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G11" s="17"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G12" s="17"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G13" s="17"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G14" s="17"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G15" s="17"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G16" s="17"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G17" s="17"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G18" s="17"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G19" s="17"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G20" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -1125,7 +1185,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
@@ -1138,7 +1198,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1164,7 +1224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1188,7 +1248,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1210,7 +1270,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1232,7 +1292,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1254,7 +1314,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1276,7 +1336,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1298,7 +1358,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1320,7 +1380,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1342,7 +1402,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1364,7 +1424,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>10</v>
       </c>

--- a/DataTables/DetailText/剧情/004老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004老师来访.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C77DF17-B8A8-45E8-8129-A770C3D66C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B310B2-6135-4E87-83A0-F2BF90BE9DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1024,20 +1024,19 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">

--- a/DataTables/DetailText/剧情/004老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004老师来访.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B310B2-6135-4E87-83A0-F2BF90BE9DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D954829B-582F-4B8F-AA66-E5D39EC428D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
   <si>
     <t>StoryID</t>
   </si>
@@ -565,6 +565,10 @@
   </si>
   <si>
     <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -639,7 +643,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -661,6 +665,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -692,7 +702,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -739,6 +749,12 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1021,25 +1037,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1052,38 +1069,41 @@
       <c r="D1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="18" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>39</v>
       </c>
@@ -1096,84 +1116,85 @@
       <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="1">
         <v>2</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="1"/>
+      <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="1" t="b">
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C3" s="10"/>
-      <c r="G3" s="17"/>
-      <c r="L3" s="11"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="H3" s="17"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C4" s="10"/>
-      <c r="G4" s="17"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="H4" s="17"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C5" s="10"/>
-      <c r="G5" s="17"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G6" s="17"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G7" s="17"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G8" s="17"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G9" s="17"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G13" s="17"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G14" s="17"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G16" s="17"/>
-    </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G17" s="17"/>
-    </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G18" s="17"/>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G19" s="17"/>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G20" s="17"/>
+      <c r="H5" s="17"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H6" s="17"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H7" s="17"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H8" s="17"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H9" s="17"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H10" s="17"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H11" s="17"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H12" s="17"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H13" s="17"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H14" s="17"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H15" s="17"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H16" s="17"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H17" s="17"/>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H18" s="17"/>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H19" s="17"/>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H20" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/004老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004老师来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D954829B-582F-4B8F-AA66-E5D39EC428D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D854DB64-8A08-43F8-81FB-59F1F483FD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="48">
   <si>
     <t>StoryID</t>
   </si>
@@ -97,12 +86,6 @@
     <t>TriggerDay</t>
   </si>
   <si>
-    <t>Reputation</t>
-  </si>
-  <si>
-    <t>EntryId</t>
-  </si>
-  <si>
     <t>NpcID</t>
   </si>
   <si>
@@ -570,17 +553,33 @@
   <si>
     <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerReputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerEntryId</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -594,7 +593,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -615,7 +614,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -759,7 +758,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1037,26 +1036,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1070,54 +1072,60 @@
         <v>15</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="K1" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="16" t="s">
+      <c r="O1" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="P1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="N1" s="18" t="s">
+      <c r="Q1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="18" t="s">
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="1">
         <v>2</v>
@@ -1131,69 +1139,71 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1" t="b">
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="O2" s="1">
+      <c r="Q2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17">
       <c r="C3" s="10"/>
       <c r="H3" s="17"/>
-      <c r="N3" s="11"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="P3" s="11"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="C4" s="10"/>
       <c r="H4" s="17"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17">
       <c r="C5" s="10"/>
       <c r="H5" s="17"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17">
       <c r="H6" s="17"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17">
       <c r="H7" s="17"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17">
       <c r="H8" s="17"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17">
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17">
       <c r="H10" s="17"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17">
       <c r="H11" s="17"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17">
       <c r="H12" s="17"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17">
       <c r="H13" s="17"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17">
       <c r="H14" s="17"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17">
       <c r="H15" s="17"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17">
       <c r="H16" s="17"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8">
       <c r="H17" s="17"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8">
       <c r="H18" s="17"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8">
       <c r="H19" s="17"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="17"/>
     </row>
   </sheetData>
@@ -1205,20 +1215,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1244,7 +1254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1252,23 +1262,23 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1276,21 +1286,21 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1298,21 +1308,21 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1320,21 +1330,21 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1342,21 +1352,21 @@
         <v>6</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1364,21 +1374,21 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1386,21 +1396,21 @@
         <v>6</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1408,21 +1418,21 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1430,21 +1440,21 @@
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1452,18 +1462,18 @@
         <v>6</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
